--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2371-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2371-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{055569A3-DEDE-4C66-9A25-87DBAE55C20B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{03977438-7106-4C9A-BA72-6DE4F0543CE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{E7BE46E7-DA7C-4DC8-92FA-7F83DB2927FE}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{17E7708E-0FB9-402F-A75D-AA85FE059E4F}"/>
   </bookViews>
   <sheets>
     <sheet name="2371-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1442,25 +1442,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC5B9FB5-A2E3-43EB-BE63-38885AE8D530}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EC161B4-FA5E-4109-9EB0-E6BD334269D0}">
   <dimension ref="A1:R53"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9.109375" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="7.5" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="11.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1488,7 +1488,7 @@
       <c r="Q1" s="31"/>
       <c r="R1" s="23"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1518,7 +1518,7 @@
       <c r="Q2" s="33"/>
       <c r="R2" s="34"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1564,7 +1564,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1614,7 +1614,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>2026</v>
       </c>
@@ -1668,7 +1668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1724,7 +1724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="40">
         <v>2025</v>
       </c>
@@ -1778,7 +1778,7 @@
         <v>7.79</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1834,7 +1834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1890,7 +1890,7 @@
         <v>7.79</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>26</v>
       </c>
@@ -1946,7 +1946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="38">
         <v>2024</v>
       </c>
@@ -2000,7 +2000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>26</v>
       </c>
@@ -2056,7 +2056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>26</v>
       </c>
@@ -2112,7 +2112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="40">
         <v>2023</v>
       </c>
@@ -2166,7 +2166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="38">
         <v>2022</v>
       </c>
@@ -2220,7 +2220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="40">
         <v>2021</v>
       </c>
@@ -2274,7 +2274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="38">
         <v>2020</v>
       </c>
@@ -2328,7 +2328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="40">
         <v>2019</v>
       </c>
@@ -2382,7 +2382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="38">
         <v>2018</v>
       </c>
@@ -2436,7 +2436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="40">
         <v>2017</v>
       </c>
@@ -2490,7 +2490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="38">
         <v>2016</v>
       </c>
@@ -2544,7 +2544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="40">
         <v>2015</v>
       </c>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="38">
         <v>2014</v>
       </c>
@@ -2652,7 +2652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="40">
         <v>2013</v>
       </c>
@@ -2706,7 +2706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="38">
         <v>2012</v>
       </c>
@@ -2760,7 +2760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="40">
         <v>2011</v>
       </c>
@@ -2814,7 +2814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="38">
         <v>2010</v>
       </c>
@@ -2868,7 +2868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="40">
         <v>2009</v>
       </c>
@@ -2922,7 +2922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="38">
         <v>2008</v>
       </c>
@@ -2976,7 +2976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="40">
         <v>2007</v>
       </c>
@@ -3030,7 +3030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="38">
         <v>2006</v>
       </c>
@@ -3084,7 +3084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="40">
         <v>2005</v>
       </c>
@@ -3138,7 +3138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="38">
         <v>2004</v>
       </c>
@@ -3192,7 +3192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="40">
         <v>2003</v>
       </c>
@@ -3246,7 +3246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="38">
         <v>2002</v>
       </c>
@@ -3300,7 +3300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="40">
         <v>2001</v>
       </c>
@@ -3354,7 +3354,7 @@
         <v>8.86</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="38">
         <v>2000</v>
       </c>
@@ -3408,7 +3408,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="40">
         <v>1999</v>
       </c>
@@ -3462,7 +3462,7 @@
         <v>2.67</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="38">
         <v>1998</v>
       </c>
@@ -3516,7 +3516,7 @@
         <v>7.31</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="40">
         <v>1997</v>
       </c>
@@ -3570,7 +3570,7 @@
         <v>6.27</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="38">
         <v>1996</v>
       </c>
@@ -3624,7 +3624,7 @@
         <v>5.34</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="40">
         <v>1995</v>
       </c>
@@ -3678,7 +3678,7 @@
         <v>5.87</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="38">
         <v>1994</v>
       </c>
@@ -3732,7 +3732,7 @@
         <v>3.23</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="40">
         <v>1993</v>
       </c>
@@ -3786,7 +3786,7 @@
         <v>5.37</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="38">
         <v>1991</v>
       </c>
@@ -3840,7 +3840,7 @@
         <v>2.89</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="40">
         <v>1990</v>
       </c>
@@ -3894,7 +3894,7 @@
         <v>2.25</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="38">
         <v>1989</v>
       </c>
@@ -3948,7 +3948,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="40">
         <v>1988</v>
       </c>
@@ -4002,7 +4002,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="38">
         <v>1987</v>
       </c>
@@ -4056,7 +4056,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="40">
         <v>1986</v>
       </c>
@@ -4110,7 +4110,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="38">
         <v>1985</v>
       </c>
@@ -4164,7 +4164,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="40">
         <v>1984</v>
       </c>
@@ -4218,7 +4218,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="38" t="s">
         <v>32</v>
       </c>
